--- a/data/trans_camb/IP28_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP28_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 4,49</t>
+          <t>-0,69; 4,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1,7</t>
+          <t>-1,87; 1,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 4,48</t>
+          <t>-0,97; 4,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 4,36</t>
+          <t>-0,97; 4,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 2,39</t>
+          <t>-1,63; 2,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 1,75</t>
+          <t>-2,01; 1,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 3,24</t>
+          <t>-0,26; 3,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 1,25</t>
+          <t>-1,38; 1,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 2,33</t>
+          <t>-0,92; 2,41</t>
         </is>
       </c>
     </row>
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>-37,67; 1185,64</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-47,05; 852,18</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 309,77</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-75,54; 656,5</t>
+          <t>-72,26; 720,77</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 0,06</t>
+          <t>-3,06; 0,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 0,96</t>
+          <t>-2,75; 0,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,82; -0,67</t>
+          <t>-4,04; -0,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 2,3</t>
+          <t>-1,48; 2,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 1,34</t>
+          <t>-2,47; 1,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 1,09</t>
+          <t>-2,22; 1,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 0,7</t>
+          <t>-1,84; 0,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 0,51</t>
+          <t>-1,98; 0,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 0,01</t>
+          <t>-2,31; 0,05</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 246,91</t>
+          <t>-100,0; 189,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1014,32 +1014,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-73,9; 358,41</t>
+          <t>-65,45; 555,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 220,26</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 319,46</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-79,52; 85,75</t>
+          <t>-77,85; 85,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-83,47; 67,65</t>
+          <t>-83,54; 63,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 27,09</t>
+          <t>-100,0; 35,91</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 3,0</t>
+          <t>-1,05; 2,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 1,52</t>
+          <t>-1,56; 1,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 4,35</t>
+          <t>-0,3; 4,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 0,75</t>
+          <t>-3,65; 0,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 1,59</t>
+          <t>-3,09; 1,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 1,47</t>
+          <t>-2,73; 1,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 1,08</t>
+          <t>-1,71; 1,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 0,97</t>
+          <t>-1,75; 1,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 2,16</t>
+          <t>-1,27; 1,96</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-81,31; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1235,27 +1235,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 505,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 454,36</t>
+          <t>-100,0; inf</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-83,96; 237,45</t>
+          <t>-81,44; 225,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-83,8; 187,2</t>
+          <t>-85,15; 198,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-64,52; 341,34</t>
+          <t>-67,45; 258,86</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 5,34</t>
+          <t>-0,41; 5,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 2,02</t>
+          <t>-2,13; 2,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 2,6</t>
+          <t>-2,03; 2,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 3,05</t>
+          <t>-0,34; 3,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,47</t>
+          <t>-1,16; 1,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,67</t>
+          <t>-1,0; 1,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 3,56</t>
+          <t>-0,04; 3,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,19</t>
+          <t>-1,19; 1,25</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,52</t>
+          <t>-1,14; 1,63</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-34,21; 1034,74</t>
+          <t>-30,55; 906,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-84,87; 483,54</t>
+          <t>-87,45; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-74,83; —</t>
+          <t>-75,12; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 685,38</t>
+          <t>-16,96; 550,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-80,09; 208,06</t>
+          <t>-75,28; 280,84</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-77,29; 305,26</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,88</t>
+          <t>-0,42; 1,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,61</t>
+          <t>-1,27; 0,61</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,27</t>
+          <t>-0,86; 1,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,52</t>
+          <t>-0,49; 1,54</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,65</t>
+          <t>-1,16; 0,61</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,65</t>
+          <t>-1,16; 0,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 1,36</t>
+          <t>-0,17; 1,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,42</t>
+          <t>-0,95; 0,29</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,58</t>
+          <t>-0,76; 0,65</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-28,36; 223,74</t>
+          <t>-24,75; 230,13</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-70,93; 81,44</t>
+          <t>-67,71; 78,22</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-56,6; 145,41</t>
+          <t>-49,61; 169,36</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-37,97; 189,97</t>
+          <t>-35,59; 211,18</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-65,58; 98,17</t>
+          <t>-71,45; 85,67</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-66,68; 90,76</t>
+          <t>-69,3; 100,05</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 142,12</t>
+          <t>-12,79; 145,75</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-56,02; 48,87</t>
+          <t>-58,49; 31,81</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-50,67; 62,43</t>
+          <t>-47,76; 65,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP28_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP28_R-Habitat-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura</t>
+          <t>Menores cuyo peso es bastante mayor de lo normal en relación con su altura</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 4,59</t>
+          <t>-0,7; 4,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 1,69</t>
+          <t>-1,84; 1,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 4,49</t>
+          <t>-0,93; 5,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 4,33</t>
+          <t>-0,89; 4,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 2,51</t>
+          <t>-1,49; 2,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 1,78</t>
+          <t>-1,88; 1,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 3,31</t>
+          <t>-0,24; 3,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,25</t>
+          <t>-1,29; 1,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 2,41</t>
+          <t>-0,87; 2,23</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,67; 1185,64</t>
+          <t>-39,22; 1023,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-72,26; 720,77</t>
+          <t>-76,94; 764,17</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 0,04</t>
+          <t>-3,36; 0,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 0,93</t>
+          <t>-2,71; 0,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,04; -0,67</t>
+          <t>-3,73; -0,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 2,52</t>
+          <t>-1,83; 2,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 1,02</t>
+          <t>-2,47; 1,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 1,11</t>
+          <t>-2,52; 1,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,84</t>
+          <t>-1,8; 0,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 0,51</t>
+          <t>-2,0; 0,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 0,05</t>
+          <t>-2,36; -0,08</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 288,26</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 189,87</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>-76,26; 329,83</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-65,45; 555,75</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 220,26</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 257,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-77,85; 85,97</t>
+          <t>-76,22; 107,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-83,54; 63,92</t>
+          <t>-84,13; 77,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 35,91</t>
+          <t>-100,0; 18,11</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 2,88</t>
+          <t>-1,07; 3,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,41</t>
+          <t>-1,67; 1,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 4,43</t>
+          <t>-0,62; 4,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 0,67</t>
+          <t>-3,3; 0,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 1,68</t>
+          <t>-3,01; 1,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 1,73</t>
+          <t>-2,9; 1,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,06</t>
+          <t>-1,61; 1,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 1,03</t>
+          <t>-1,71; 1,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 1,96</t>
+          <t>-1,16; 2,02</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-81,31; —</t>
+          <t>-94,91; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1235,27 +1235,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 505,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; inf</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-81,44; 225,93</t>
+          <t>-82,13; 227,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-85,15; 198,12</t>
+          <t>-83,16; 213,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-67,45; 258,86</t>
+          <t>-63,42; 275,55</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 5,2</t>
+          <t>-0,59; 5,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 2,28</t>
+          <t>-2,42; 1,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 2,68</t>
+          <t>-2,03; 2,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 3,03</t>
+          <t>-0,39; 2,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,43</t>
+          <t>-1,22; 1,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,81</t>
+          <t>-1,18; 1,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 3,33</t>
+          <t>0,04; 3,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 1,25</t>
+          <t>-1,19; 1,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 1,63</t>
+          <t>-1,23; 1,47</t>
         </is>
       </c>
     </row>
@@ -1431,24 +1431,24 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-30,55; 906,3</t>
+          <t>-40,3; 983,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-87,45; —</t>
+          <t>-89,9; 396,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>-93,35; 580,84</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>-75,12; —</t>
-        </is>
-      </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-16,96; 550,66</t>
+          <t>-11,71; 665,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-75,28; 280,84</t>
+          <t>-75,24; 269,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-77,29; 305,26</t>
+          <t>-75,52; 319,97</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 1,95</t>
+          <t>-0,46; 1,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,61</t>
+          <t>-1,31; 0,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,44</t>
+          <t>-1,04; 1,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,54</t>
+          <t>-0,57; 1,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,61</t>
+          <t>-1,17; 0,72</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,67</t>
+          <t>-1,21; 0,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,36</t>
+          <t>-0,25; 1,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,29</t>
+          <t>-0,87; 0,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,65</t>
+          <t>-0,8; 0,65</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-24,75; 230,13</t>
+          <t>-24,71; 241,5</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-67,71; 78,22</t>
+          <t>-68,68; 70,9</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-49,61; 169,36</t>
+          <t>-59,15; 185,97</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-35,59; 211,18</t>
+          <t>-33,66; 181,56</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-71,45; 85,67</t>
+          <t>-66,43; 103,37</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-69,3; 100,05</t>
+          <t>-69,64; 104,99</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 145,75</t>
+          <t>-15,53; 141,25</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-58,49; 31,81</t>
+          <t>-53,93; 48,68</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-47,76; 65,16</t>
+          <t>-50,51; 67,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP28_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP28_R-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,24</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,16</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,05</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1,34</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-0,34</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,14</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,24</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,16</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,01</t>
+          <t>1,18</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,6</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 4,4</t>
+          <t>-0,78; 4,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1,62</t>
+          <t>-1,57; 2,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 5,03</t>
+          <t>-1,78; 2,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 4,27</t>
+          <t>-0,81; 4,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,77</t>
+          <t>-1,84; 1,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 1,67</t>
+          <t>-1,0; 4,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 3,49</t>
+          <t>-0,22; 3,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 1,2</t>
+          <t>-1,4; 1,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,23</t>
+          <t>-0,87; 2,5</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>131,54%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17,42%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,52%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>147,02%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-37,58%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>124,99%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>131,54%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>17,42%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-1,51%</t>
+          <t>129,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>64,67%</t>
         </is>
       </c>
     </row>
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,22; 1023,65</t>
+          <t>-47,05; 852,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 309,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-76,94; 764,17</t>
+          <t>-73,95; 706,67</t>
         </is>
       </c>
     </row>
@@ -840,34 +840,34 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,31</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,59</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-0,58</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-1,32</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,71</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>-1,69</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,31</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,59</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-0,62</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t>-0,46</t>
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,08</t>
+          <t>-1,07</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 0,05</t>
+          <t>-1,63; 2,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 0,96</t>
+          <t>-2,29; 1,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,73; -0,67</t>
+          <t>-2,33; 1,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 2,33</t>
+          <t>-3,33; 0,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 1,01</t>
+          <t>-2,72; 0,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 1,1</t>
+          <t>-3,82; -0,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 0,85</t>
+          <t>-1,8; 0,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,5</t>
+          <t>-2,28; 0,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,36; -0,08</t>
+          <t>-2,32; 0,06</t>
         </is>
       </c>
     </row>
@@ -946,34 +946,34 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19,54%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-37,43%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-36,7%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-78,38%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-42,21%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>19,54%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-37,43%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-39,28%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>-28,35%</t>
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-66,37%</t>
+          <t>-65,55%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-73,9; 358,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 288,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 348,34</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-76,26; 329,83</t>
-        </is>
-      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 246,91</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 257,2</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-76,22; 107,13</t>
+          <t>-79,52; 85,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-84,13; 77,52</t>
+          <t>-83,47; 67,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 18,11</t>
+          <t>-100,0; 26,87</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,05</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,56</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-0,46</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,6</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-0,01</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,52</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,05</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,56</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,58</t>
+          <t>2,14</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,79</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 3,06</t>
+          <t>-3,34; 0,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 1,24</t>
+          <t>-2,94; 1,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 4,19</t>
+          <t>-2,92; 1,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 0,72</t>
+          <t>-0,89; 3,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 1,6</t>
+          <t>-1,7; 1,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 1,82</t>
+          <t>-0,03; 5,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 1,12</t>
+          <t>-1,61; 1,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,03</t>
+          <t>-1,67; 0,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 2,02</t>
+          <t>-0,97; 2,73</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-57,25%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-30,6%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-25,34%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>77,95%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-1,09%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>196,33%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-57,25%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-30,6%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-31,4%</t>
+          <t>275,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>59,15%</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-94,91; —</t>
+          <t>-100,0; 513,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-82,13; 227,9</t>
+          <t>-83,96; 237,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-83,16; 213,06</t>
+          <t>-83,8; 187,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-63,42; 275,55</t>
+          <t>-57,19; 431,06</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,05</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,05</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,02</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2,28</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,09</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,08</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,05</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>0,31</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,16</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 5,28</t>
+          <t>-0,33; 3,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 1,89</t>
+          <t>-0,99; 1,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 2,96</t>
+          <t>-1,04; 1,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 2,84</t>
+          <t>-0,15; 5,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,76</t>
+          <t>-2,16; 2,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,58</t>
+          <t>-1,86; 2,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 3,37</t>
+          <t>0,15; 3,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 1,2</t>
+          <t>-1,41; 1,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,47</t>
+          <t>-1,33; 1,63</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>160,65%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7,07%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>142,66%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-5,55%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>160,65%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>7,07%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-40,3; 983,59</t>
+          <t>-74,83; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-89,9; 396,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-93,35; 580,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
+          <t>-34,21; 1034,74</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>-84,87; 483,54</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>-2,23; 685,38</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>-80,09; 208,06</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-11,71; 665,73</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-75,24; 269,23</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>-75,52; 319,97</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,43</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,23</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-0,22</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,7</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-0,31</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,43</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,23</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>0,03</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,8</t>
+          <t>-0,58; 1,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,57</t>
+          <t>-1,17; 0,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 1,35</t>
+          <t>-1,08; 0,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,45</t>
+          <t>-0,39; 1,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,72</t>
+          <t>-1,28; 0,61</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 0,67</t>
+          <t>-0,79; 1,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,35</t>
+          <t>-0,16; 1,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,41</t>
+          <t>-0,86; 0,42</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,65</t>
+          <t>-0,71; 0,75</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>34,55%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-18,93%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-18,07%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>53,31%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-23,6%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>9,32%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>34,55%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-18,93%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-20,2%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-6,05%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-24,71; 241,5</t>
+          <t>-37,97; 189,97</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-68,68; 70,9</t>
+          <t>-65,58; 98,17</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-59,15; 185,97</t>
+          <t>-65,21; 103,72</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-33,66; 181,56</t>
+          <t>-28,36; 223,74</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-66,43; 103,37</t>
+          <t>-70,93; 81,44</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-69,64; 104,99</t>
+          <t>-48,76; 184,05</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-15,53; 141,25</t>
+          <t>-12,35; 142,12</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-53,93; 48,68</t>
+          <t>-56,02; 48,87</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-50,51; 67,59</t>
+          <t>-45,56; 78,14</t>
         </is>
       </c>
     </row>
